--- a/src/test/fixtures/forms-responses-http/export-state-rejected-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-rejected-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>TCEC9568D-000004</x:t>
+    <x:t>T80592E4F-000004</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-rejected-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-rejected-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T80592E4F-000004</x:t>
+    <x:t>TC4458834-000004</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-rejected-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-rejected-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>TC4458834-000004</x:t>
+    <x:t>T28739888-000004</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-rejected-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-rejected-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T28739888-000004</x:t>
+    <x:t>TF41A6DDC-000004</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-rejected-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-rejected-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>TF41A6DDC-000004</x:t>
+    <x:t>T3DE5668D-000004</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-rejected-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-rejected-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T3DE5668D-000004</x:t>
+    <x:t>T863A7CE2-000004</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-rejected-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-rejected-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T863A7CE2-000004</x:t>
+    <x:t>TA2B595C4-000004</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-rejected-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-rejected-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>TA2B595C4-000004</x:t>
+    <x:t>T1857CACC-000004</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-rejected-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-rejected-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T1857CACC-000004</x:t>
+    <x:t>T1A40E40A-000004</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-rejected-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-rejected-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T1A40E40A-000004</x:t>
+    <x:t>T8FA97197-000004</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-rejected-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-rejected-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T8FA97197-000004</x:t>
+    <x:t>T057A7199-000004</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
